--- a/spec/new-btg-devops-task-list.xlsx
+++ b/spec/new-btg-devops-task-list.xlsx
@@ -172,7 +172,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="13" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
@@ -240,6 +240,7 @@
     <xf numFmtId="0" fontId="0" fillId="13" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -605,7 +606,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J66"/>
+  <dimension ref="A1:J74"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelRow="0"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -3272,274 +3273,674 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="4" t="inlineStr">
+      <c r="A60" s="5" t="n">
+        <v>52</v>
+      </c>
+      <c r="B60" s="5" t="inlineStr">
+        <is>
+          <t>Phase 6 · Cost &amp; Usage Data Integrity</t>
+        </is>
+      </c>
+      <c r="C60" s="6" t="inlineStr">
+        <is>
+          <t>Fix cross-audit finding-matching key</t>
+        </is>
+      </c>
+      <c r="D60" s="7" t="inlineStr">
+        <is>
+          <t>findingKey() = resource_type|resource_name|category breaks when the LLM re-groups resource_name text or re-categorizes the same issue between audits, causing false resolve-then-recreate cycles. Confirmed root cause of the "$ Saved" card showing $3,967 in savings none of which were real (5/5 spot-checked resources still exist unchanged in Azure).</t>
+        </is>
+      </c>
+      <c r="E60" s="5" t="inlineStr">
+        <is>
+          <t>Dev B</t>
+        </is>
+      </c>
+      <c r="F60" s="5" t="inlineStr">
+        <is>
+          <t>Task 51</t>
+        </is>
+      </c>
+      <c r="G60" s="5" t="inlineStr">
+        <is>
+          <t>2 days</t>
+        </is>
+      </c>
+      <c r="H60" s="8" t="inlineStr">
+        <is>
+          <t>✅ Done</t>
+        </is>
+      </c>
+      <c r="I60" s="5" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J60" s="7" t="inlineStr">
+        <is>
+          <t>claude.ts:216-218 saveFindings/findingKey; key on individual resource identity (not the LLM-grouped display string) and drop or stabilize category from the key</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="5" t="n">
+        <v>53</v>
+      </c>
+      <c r="B61" s="5" t="inlineStr">
+        <is>
+          <t>Phase 6 · Cost &amp; Usage Data Integrity</t>
+        </is>
+      </c>
+      <c r="C61" s="6" t="inlineStr">
+        <is>
+          <t>Fix silent truncation: Zombie Spend / Cost by Resource Group / Cost by Tag</t>
+        </is>
+      </c>
+      <c r="D61" s="7" t="inlineStr">
+        <is>
+          <t>SIGNAL_MAX_ZOMBIE_SPEND=20 (actual 47, $78.67 hidden), SIGNAL_MAX_ROLLUP_ROWS=15 for both resource-group (actual 45 groups, ~30 hidden incl. $70+ ones) and tag rollups (actual 101, 86 hidden) all silently slice with no "of N" indicator shown anywhere.</t>
+        </is>
+      </c>
+      <c r="E61" s="5" t="inlineStr">
+        <is>
+          <t>Dev B</t>
+        </is>
+      </c>
+      <c r="F61" s="5" t="inlineStr">
+        <is>
+          <t>Task 51</t>
+        </is>
+      </c>
+      <c r="G61" s="5" t="inlineStr">
+        <is>
+          <t>1.5 days</t>
+        </is>
+      </c>
+      <c r="H61" s="8" t="inlineStr">
+        <is>
+          <t>✅ Done</t>
+        </is>
+      </c>
+      <c r="I61" s="5" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J61" s="7" t="inlineStr">
+        <is>
+          <t>audit.ts:74-78,172-178; add _truncated booleans per signal (mirror resources_truncated) and show "top N of M" in ZombieSpendList/CostBreakdownTabs</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="5" t="n">
+        <v>54</v>
+      </c>
+      <c r="B62" s="5" t="inlineStr">
+        <is>
+          <t>Phase 6 · Cost &amp; Usage Data Integrity</t>
+        </is>
+      </c>
+      <c r="C62" s="6" t="inlineStr">
+        <is>
+          <t>Wire up existing resources_truncated flag in UI</t>
+        </is>
+      </c>
+      <c r="D62" s="7" t="inlineStr">
+        <is>
+          <t>resources_truncated is already computed correctly (audit.ts:192) and typed on CostSummary, but no component anywhere reads it — dead field, so even the one signal that already tracks its own truncation shows nothing to the user today.</t>
+        </is>
+      </c>
+      <c r="E62" s="5" t="inlineStr">
+        <is>
+          <t>Dev B</t>
+        </is>
+      </c>
+      <c r="F62" s="5" t="inlineStr">
+        <is>
+          <t>Task 53</t>
+        </is>
+      </c>
+      <c r="G62" s="5" t="inlineStr">
+        <is>
+          <t>0.5 day</t>
+        </is>
+      </c>
+      <c r="H62" s="8" t="inlineStr">
+        <is>
+          <t>✅ Done</t>
+        </is>
+      </c>
+      <c r="I62" s="5" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="J62" s="7" t="inlineStr">
+        <is>
+          <t>grep confirmed zero reads of resources_truncated in app/components</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="5" t="n">
+        <v>55</v>
+      </c>
+      <c r="B63" s="5" t="inlineStr">
+        <is>
+          <t>Phase 6 · Cost &amp; Usage Data Integrity</t>
+        </is>
+      </c>
+      <c r="C63" s="6" t="inlineStr">
+        <is>
+          <t>Verify Idle Resources detector output</t>
+        </is>
+      </c>
+      <c r="D63" s="7" t="inlineStr">
+        <is>
+          <t>detectIdleResources (usageInsights.ts IDLE_RULES) not yet cross-checked against raw usage_data the way Zombie Spend / Cost Breakdown were. Confirm thresholds (Cosmos RU&lt;10%, App Service CPU/Mem&lt;5%, zero-total checks) produce sane results and the 30-item cap doesn't hide meaningful entries on real audits.</t>
+        </is>
+      </c>
+      <c r="E63" s="5" t="inlineStr">
+        <is>
+          <t>Dev B</t>
+        </is>
+      </c>
+      <c r="F63" s="5" t="inlineStr">
+        <is>
+          <t>Task 51</t>
+        </is>
+      </c>
+      <c r="G63" s="5" t="inlineStr">
+        <is>
+          <t>1 day</t>
+        </is>
+      </c>
+      <c r="H63" s="8" t="inlineStr">
+        <is>
+          <t>✅ Done</t>
+        </is>
+      </c>
+      <c r="I63" s="5" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="J63" s="7" t="inlineStr">
+        <is>
+          <t>Same recompute-and-diff method used for zombie spend/cost breakdown this session</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="5" t="n">
+        <v>56</v>
+      </c>
+      <c r="B64" s="5" t="inlineStr">
+        <is>
+          <t>Phase 6 · Cost &amp; Usage Data Integrity</t>
+        </is>
+      </c>
+      <c r="C64" s="6" t="inlineStr">
+        <is>
+          <t>Verify LLM-input-only signals: Service Concentration, Cost/Usage Waste, RI Candidates</t>
+        </is>
+      </c>
+      <c r="D64" s="7" t="inlineStr">
+        <is>
+          <t>These three detectors are never shown directly in the UI — they only feed buildPrecomputedSignals (claude.ts) as "facts" the agent treats as ground truth. A bug here is more dangerous than a display bug: it would silently poison the AI's findings rather than just showing a wrong number.</t>
+        </is>
+      </c>
+      <c r="E64" s="5" t="inlineStr">
+        <is>
+          <t>Dev B</t>
+        </is>
+      </c>
+      <c r="F64" s="5" t="inlineStr">
+        <is>
+          <t>Task 51</t>
+        </is>
+      </c>
+      <c r="G64" s="5" t="inlineStr">
+        <is>
+          <t>1.5 days</t>
+        </is>
+      </c>
+      <c r="H64" s="8" t="inlineStr">
+        <is>
+          <t>✅ Done</t>
+        </is>
+      </c>
+      <c r="I64" s="5" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J64" s="7" t="inlineStr">
+        <is>
+          <t>costInsights.ts detectServiceConcentration/detectCostUsageWaste/detectReservedInstanceCandidates, consumed only via claude.ts buildPrecomputedSignals</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="5" t="n">
+        <v>57</v>
+      </c>
+      <c r="B65" s="5" t="inlineStr">
+        <is>
+          <t>Phase 6 · Cost &amp; Usage Data Integrity</t>
+        </is>
+      </c>
+      <c r="C65" s="6" t="inlineStr">
+        <is>
+          <t>Investigate Resources Sampled count mismatch</t>
+        </is>
+      </c>
+      <c r="D65" s="7" t="inlineStr">
+        <is>
+          <t>Cost &amp; Usage page shows "Resources Sampled: 99" (CLI's own usage_data.total_resources_sampled counter) but only 94 distinct resource_ids actually appear in the stored metrics array for the same audit — a 5-resource gap in the CLI's own counting logic.</t>
+        </is>
+      </c>
+      <c r="E65" s="5" t="inlineStr">
+        <is>
+          <t>Dev A</t>
+        </is>
+      </c>
+      <c r="F65" s="5" t="inlineStr">
+        <is>
+          <t>Task 51</t>
+        </is>
+      </c>
+      <c r="G65" s="5" t="inlineStr">
+        <is>
+          <t>0.5 day</t>
+        </is>
+      </c>
+      <c r="H65" s="8" t="inlineStr">
+        <is>
+          <t>✅ Done</t>
+        </is>
+      </c>
+      <c r="I65" s="5" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="J65" s="7" t="inlineStr">
+        <is>
+          <t>CLI Engine usage collection — total_resources_sampled counter vs. actual metrics rows written</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="5" t="n">
+        <v>58</v>
+      </c>
+      <c r="B66" s="5" t="inlineStr">
+        <is>
+          <t>Phase 6 · Cost &amp; Usage Data Integrity</t>
+        </is>
+      </c>
+      <c r="C66" s="6" t="inlineStr">
+        <is>
+          <t>Add unit tests for costInsights.ts / usageInsights.ts detectors</t>
+        </is>
+      </c>
+      <c r="D66" s="7" t="inlineStr">
+        <is>
+          <t>Zero automated test coverage exists today for any of the deterministic cost/usage functions (no .test.ts/.spec.ts files, no jest/vitest configured in dashboard/package.json) — root cause of why the truncation and finding-matching bugs went unnoticed until manual verification this session.</t>
+        </is>
+      </c>
+      <c r="E66" s="5" t="inlineStr">
+        <is>
+          <t>Dev B</t>
+        </is>
+      </c>
+      <c r="F66" s="5" t="inlineStr">
+        <is>
+          <t>Tasks 52,53,55,56</t>
+        </is>
+      </c>
+      <c r="G66" s="5" t="inlineStr">
+        <is>
+          <t>2 days</t>
+        </is>
+      </c>
+      <c r="H66" s="8" t="inlineStr">
+        <is>
+          <t>✅ Done</t>
+        </is>
+      </c>
+      <c r="I66" s="5" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J66" s="7" t="inlineStr">
+        <is>
+          <t>Regression-prevention task — pin known-good fixtures (real audit cost_data/usage_data snapshots) as test inputs</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="5" t="n">
+        <v>59</v>
+      </c>
+      <c r="B67" s="5" t="inlineStr">
+        <is>
+          <t>Phase 6 · Cost &amp; Usage Data Integrity</t>
+        </is>
+      </c>
+      <c r="C67" s="6" t="inlineStr">
+        <is>
+          <t>Fix resource-group/tag casing collisions in cost rollups</t>
+        </is>
+      </c>
+      <c r="D67" s="7" t="inlineStr">
+        <is>
+          <t>Found while comparing Task 53's fix against a fresh real audit: the SAME real resource group/tag was recorded with different casing across different resources' inventory records (e.g. "BistecCare-Ltd-PROD" vs "bisteccare-ltd-prod", "Environment" vs "environment") — rollupCostByResourceGroup/rollupCostByTag silently split cost and resource counts across duplicate rows for what Azure treats as one group. Confirmed on live data: merging cut resource-group count from 45 to 41 and correctly combined $1267.41/2 resources + $793.50/17 resources into one $2060.91/19-resource row.</t>
+        </is>
+      </c>
+      <c r="E67" s="5" t="inlineStr">
+        <is>
+          <t>Dev B</t>
+        </is>
+      </c>
+      <c r="F67" s="5" t="inlineStr">
+        <is>
+          <t>Task 53</t>
+        </is>
+      </c>
+      <c r="G67" s="5" t="inlineStr">
+        <is>
+          <t>0.5 day</t>
+        </is>
+      </c>
+      <c r="H67" s="8" t="inlineStr">
+        <is>
+          <t>✅ Done</t>
+        </is>
+      </c>
+      <c r="I67" s="5" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J67" s="7" t="inlineStr">
+        <is>
+          <t>costInsights.ts rollupCostByResourceGroup/rollupCostByTag — now key case-insensitively, first-seen casing wins for display; regression tests added to costInsights.test.ts</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">  Future Scope</t>
         </is>
       </c>
     </row>
-    <row r="61">
-      <c r="A61" s="14" t="inlineStr">
+    <row r="69">
+      <c r="A69" s="14" t="inlineStr">
         <is>
           <t>F1</t>
         </is>
       </c>
-      <c r="B61" s="14" t="inlineStr">
+      <c r="B69" s="14" t="inlineStr">
         <is>
           <t>Phase 3 · Future</t>
         </is>
       </c>
-      <c r="C61" s="15" t="inlineStr">
+      <c r="C69" s="15" t="inlineStr">
         <is>
           <t>Slack Integration</t>
         </is>
       </c>
-      <c r="D61" s="16" t="inlineStr">
+      <c r="D69" s="16" t="inlineStr">
         <is>
           <t>Post audit findings and critical alerts to DevOps team channel automatically.</t>
         </is>
       </c>
-      <c r="E61" s="14" t="inlineStr">
+      <c r="E69" s="14" t="inlineStr">
         <is>
           <t>TBD</t>
         </is>
       </c>
-      <c r="F61" s="14" t="inlineStr">
+      <c r="F69" s="14" t="inlineStr">
         <is>
           <t>Phase 2</t>
         </is>
       </c>
-      <c r="G61" s="14" t="inlineStr">
+      <c r="G69" s="14" t="inlineStr">
         <is>
           <t>3 days</t>
         </is>
       </c>
-      <c r="H61" s="17" t="inlineStr">
+      <c r="H69" s="17" t="inlineStr">
         <is>
           <t>⏳ Future</t>
         </is>
       </c>
-      <c r="I61" s="14" t="inlineStr">
+      <c r="I69" s="14" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="J61" s="16" t="inlineStr">
+      <c r="J69" s="16" t="inlineStr">
         <is>
           <t>Requires stable audit rules</t>
         </is>
       </c>
     </row>
-    <row r="62">
-      <c r="A62" s="14" t="inlineStr">
+    <row r="70">
+      <c r="A70" s="14" t="inlineStr">
         <is>
           <t>F2</t>
         </is>
       </c>
-      <c r="B62" s="14" t="inlineStr">
+      <c r="B70" s="14" t="inlineStr">
         <is>
           <t>Phase 3 · Future</t>
         </is>
       </c>
-      <c r="C62" s="15" t="inlineStr">
+      <c r="C70" s="15" t="inlineStr">
         <is>
           <t>Drift Detection</t>
         </is>
       </c>
-      <c r="D62" s="16" t="inlineStr">
+      <c r="D70" s="16" t="inlineStr">
         <is>
           <t>btg-devops drift — detect differences between IaC and live Azure configuration.</t>
         </is>
       </c>
-      <c r="E62" s="14" t="inlineStr">
+      <c r="E70" s="14" t="inlineStr">
         <is>
           <t>Dev A</t>
         </is>
       </c>
-      <c r="F62" s="14" t="inlineStr">
+      <c r="F70" s="14" t="inlineStr">
         <is>
           <t>Phase 2</t>
         </is>
       </c>
-      <c r="G62" s="14" t="inlineStr">
+      <c r="G70" s="14" t="inlineStr">
         <is>
           <t>5 days</t>
         </is>
       </c>
-      <c r="H62" s="17" t="inlineStr">
+      <c r="H70" s="17" t="inlineStr">
         <is>
           <t>⏳ Future</t>
         </is>
       </c>
-      <c r="I62" s="14" t="inlineStr">
+      <c r="I70" s="14" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="J62" s="16" t="inlineStr">
+      <c r="J70" s="16" t="inlineStr">
         <is>
           <t>Requires IaC inventory</t>
         </is>
       </c>
     </row>
-    <row r="63">
-      <c r="A63" s="14" t="inlineStr">
+    <row r="71">
+      <c r="A71" s="14" t="inlineStr">
         <is>
           <t>F3</t>
         </is>
       </c>
-      <c r="B63" s="14" t="inlineStr">
+      <c r="B71" s="14" t="inlineStr">
         <is>
           <t>Phase 3 · Future</t>
         </is>
       </c>
-      <c r="C63" s="15" t="inlineStr">
+      <c r="C71" s="15" t="inlineStr">
         <is>
           <t>Runbook Library</t>
         </is>
       </c>
-      <c r="D63" s="16" t="inlineStr">
+      <c r="D71" s="16" t="inlineStr">
         <is>
           <t>Searchable operational runbooks inside the dashboard.</t>
         </is>
       </c>
-      <c r="E63" s="14" t="inlineStr">
+      <c r="E71" s="14" t="inlineStr">
         <is>
           <t>Dev B</t>
         </is>
       </c>
-      <c r="F63" s="14" t="inlineStr">
+      <c r="F71" s="14" t="inlineStr">
         <is>
           <t>Phase 2</t>
         </is>
       </c>
-      <c r="G63" s="14" t="inlineStr">
+      <c r="G71" s="14" t="inlineStr">
         <is>
           <t>4 days</t>
         </is>
       </c>
-      <c r="H63" s="17" t="inlineStr">
+      <c r="H71" s="17" t="inlineStr">
         <is>
           <t>⏳ Future</t>
         </is>
       </c>
-      <c r="I63" s="14" t="inlineStr">
+      <c r="I71" s="14" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="J63" s="16" t="inlineStr">
+      <c r="J71" s="16" t="inlineStr">
         <is>
           <t>Requires runbook authoring process</t>
         </is>
       </c>
     </row>
-    <row r="64">
-      <c r="A64" s="14" t="inlineStr">
+    <row r="72">
+      <c r="A72" s="14" t="inlineStr">
         <is>
           <t>F4</t>
         </is>
       </c>
-      <c r="B64" s="14" t="inlineStr">
+      <c r="B72" s="14" t="inlineStr">
         <is>
           <t>Phase 3 · Future</t>
         </is>
       </c>
-      <c r="C64" s="15" t="inlineStr">
+      <c r="C72" s="15" t="inlineStr">
         <is>
           <t>Cross-region detector</t>
         </is>
       </c>
-      <c r="D64" s="16" t="inlineStr">
+      <c r="D72" s="16" t="inlineStr">
         <is>
           <t>Specific Claude prompt focus to detect resources in different regions calling each other.</t>
         </is>
       </c>
-      <c r="E64" s="14" t="inlineStr">
+      <c r="E72" s="14" t="inlineStr">
         <is>
           <t>Dev A</t>
         </is>
       </c>
-      <c r="F64" s="14" t="inlineStr">
+      <c r="F72" s="14" t="inlineStr">
         <is>
           <t>Task 25</t>
         </is>
       </c>
-      <c r="G64" s="14" t="inlineStr">
+      <c r="G72" s="14" t="inlineStr">
         <is>
           <t>2 days</t>
         </is>
       </c>
-      <c r="H64" s="17" t="inlineStr">
+      <c r="H72" s="17" t="inlineStr">
         <is>
           <t>⏳ Future</t>
         </is>
       </c>
-      <c r="I64" s="14" t="inlineStr">
+      <c r="I72" s="14" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="J64" s="16" t="inlineStr">
+      <c r="J72" s="16" t="inlineStr">
         <is>
           <t>Catches cases like the $200/month cross-region example</t>
         </is>
       </c>
     </row>
-    <row r="65">
-      <c r="A65" s="4" t="inlineStr">
+    <row r="73">
+      <c r="A73" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">  Architecture History</t>
         </is>
       </c>
     </row>
-    <row r="66">
-      <c r="A66" s="9" t="inlineStr">
+    <row r="74">
+      <c r="A74" s="9" t="inlineStr">
         <is>
           <t>H1</t>
         </is>
       </c>
-      <c r="B66" s="9" t="inlineStr">
+      <c r="B74" s="9" t="inlineStr">
         <is>
           <t>History</t>
         </is>
       </c>
-      <c r="C66" s="10" t="inlineStr">
+      <c r="C74" s="10" t="inlineStr">
         <is>
           <t>MCP Server (cmd/mcp.go)</t>
         </is>
       </c>
-      <c r="D66" s="11" t="inlineStr">
+      <c r="D74" s="11" t="inlineStr">
         <is>
           <t>Original Go-based MCP server concept.</t>
         </is>
       </c>
-      <c r="E66" s="9" t="inlineStr">
+      <c r="E74" s="9" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F66" s="9" t="inlineStr">
+      <c r="F74" s="9" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G66" s="9" t="inlineStr">
+      <c r="G74" s="9" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H66" s="18" t="inlineStr">
+      <c r="H74" s="18" t="inlineStr">
         <is>
           <t>❌ Removed</t>
         </is>
       </c>
-      <c r="I66" s="9" t="inlineStr">
+      <c r="I74" s="9" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J66" s="11" t="inlineStr">
+      <c r="J74" s="11" t="inlineStr">
         <is>
           <t>Removed 2026-06-30 in favor of direct Claude API; REINSTATED 2026-07 as dashboard/app/api/mcp per Spec 8, for a different purpose (Claude Code subscription orchestration, not a Go binary)</t>
         </is>
@@ -3551,11 +3952,11 @@
     <mergeCell ref="A31:J31"/>
     <mergeCell ref="A12:J12"/>
     <mergeCell ref="A4:J4"/>
-    <mergeCell ref="A65:J65"/>
     <mergeCell ref="A24:J24"/>
     <mergeCell ref="A2:J2"/>
-    <mergeCell ref="A60:J60"/>
+    <mergeCell ref="A73:J73"/>
     <mergeCell ref="A41:J41"/>
+    <mergeCell ref="A68:J68"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3567,7 +3968,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G16"/>
+  <dimension ref="A1:G17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelRow="0"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -3795,98 +4196,128 @@
     <row r="10">
       <c r="A10" s="21" t="inlineStr">
         <is>
-          <t>Phase 3 · Future</t>
+          <t>Phase 6 · Cost &amp; Usage Data Integrity</t>
         </is>
       </c>
       <c r="B10" s="21" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="C10" s="21" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="D10" s="21" t="n">
         <v>0</v>
       </c>
       <c r="E10" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" s="21" t="inlineStr">
+        <is>
+          <t>9.5 days</t>
+        </is>
+      </c>
+      <c r="G10" s="21" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="21" t="inlineStr">
+        <is>
+          <t>Phase 3 · Future</t>
+        </is>
+      </c>
+      <c r="B11" s="21" t="n">
         <v>4</v>
       </c>
-      <c r="F10" s="21" t="inlineStr">
+      <c r="C11" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="D11" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="E11" s="21" t="n">
+        <v>4</v>
+      </c>
+      <c r="F11" s="21" t="inlineStr">
         <is>
           <t>14 days</t>
         </is>
       </c>
-      <c r="G10" s="21" t="inlineStr">
+      <c r="G11" s="21" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="22" t="inlineStr">
+    <row r="12">
+      <c r="A12" s="22" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B11" s="22" t="n">
-        <v>55</v>
-      </c>
-      <c r="C11" s="22" t="n">
-        <v>48</v>
-      </c>
-      <c r="D11" s="22" t="n">
+      <c r="B12" s="22" t="n">
+        <v>63</v>
+      </c>
+      <c r="C12" s="22" t="n">
+        <v>56</v>
+      </c>
+      <c r="D12" s="22" t="n">
         <v>3</v>
       </c>
-      <c r="E11" s="22" t="n">
+      <c r="E12" s="22" t="n">
         <v>4</v>
       </c>
-      <c r="F11" s="22" t="inlineStr">
-        <is>
-          <t>88 days</t>
-        </is>
-      </c>
-      <c r="G11" s="22" t="inlineStr">
-        <is>
-          <t>87%</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="22" t="inlineStr">
+      <c r="F12" s="22" t="inlineStr">
+        <is>
+          <t>97.5 days</t>
+        </is>
+      </c>
+      <c r="G12" s="22" t="inlineStr">
+        <is>
+          <t>89%</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="22" t="inlineStr">
         <is>
           <t>Status Legend</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="23" t="inlineStr">
-        <is>
-          <t>✅ Done</t>
-        </is>
-      </c>
-      <c r="B14" s="24" t="inlineStr">
+    <row r="15" ht="90" customHeight="1">
+      <c r="A15" s="23" t="inlineStr">
+        <is>
+          <t>✅ Done</t>
+        </is>
+      </c>
+      <c r="B15" s="29" t="inlineStr">
         <is>
           <t>🔲 Pending</t>
         </is>
       </c>
-      <c r="C14" s="25" t="inlineStr">
+      <c r="C15" s="29" t="inlineStr">
         <is>
           <t>⚠ Blocked</t>
         </is>
       </c>
-      <c r="D14" s="26" t="inlineStr">
+      <c r="D15" s="29" t="inlineStr">
         <is>
           <t>⏳ Future</t>
         </is>
       </c>
-      <c r="E14" s="27" t="inlineStr">
+      <c r="E15" s="29" t="inlineStr">
         <is>
           <t>❌ Removed</t>
         </is>
       </c>
-    </row>
-    <row r="15" ht="90" customHeight="1"/>
-    <row r="16">
-      <c r="A16" s="28" t="inlineStr">
+      <c r="F15" s="29" t="n"/>
+      <c r="G15" s="29" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="28" t="inlineStr">
         <is>
           <t>Architecture Update (2026-07-09): The 2026-06-30 decision to remove the MCP server was reversed. Per spec/handoff/08-mcp-claude-orchestrator.md, Analyze now runs via an MCP server (dashboard/app/api/mcp) + a scheduled Claude Code cloud agent, using the existing Claude Pro/Max subscription quota instead of a metered API key (not budgeted) or free-tier models (unreliable — a free OpenRouter model produced garbled JSON in a prior production incident). Chat is unaffected and still defaults to free models. The one open gap: no scheduled cloud agent has actually been configured yet to consume the analysis_requests queue (Task 24).</t>
         </is>
@@ -3895,7 +4326,7 @@
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:G1"/>
-    <mergeCell ref="A15:G15"/>
+    <mergeCell ref="A17:G17"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
